--- a/03_lms_events.xlsx
+++ b/03_lms_events.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="68">
   <si>
     <t>event_id</t>
   </si>
@@ -131,6 +131,90 @@
   </si>
   <si>
     <t>E0022</t>
+  </si>
+  <si>
+    <t>E0023</t>
+  </si>
+  <si>
+    <t>E0024</t>
+  </si>
+  <si>
+    <t>E0025</t>
+  </si>
+  <si>
+    <t>E0026</t>
+  </si>
+  <si>
+    <t>E0027</t>
+  </si>
+  <si>
+    <t>E0028</t>
+  </si>
+  <si>
+    <t>E0029</t>
+  </si>
+  <si>
+    <t>E0030</t>
+  </si>
+  <si>
+    <t>E0031</t>
+  </si>
+  <si>
+    <t>E0032</t>
+  </si>
+  <si>
+    <t>E0033</t>
+  </si>
+  <si>
+    <t>E0034</t>
+  </si>
+  <si>
+    <t>E0035</t>
+  </si>
+  <si>
+    <t>E0036</t>
+  </si>
+  <si>
+    <t>E0037</t>
+  </si>
+  <si>
+    <t>E0038</t>
+  </si>
+  <si>
+    <t>E0039</t>
+  </si>
+  <si>
+    <t>E0040</t>
+  </si>
+  <si>
+    <t>E0041</t>
+  </si>
+  <si>
+    <t>E0042</t>
+  </si>
+  <si>
+    <t>E0043</t>
+  </si>
+  <si>
+    <t>E0044</t>
+  </si>
+  <si>
+    <t>E0045</t>
+  </si>
+  <si>
+    <t>E0046</t>
+  </si>
+  <si>
+    <t>E0047</t>
+  </si>
+  <si>
+    <t>E0048</t>
+  </si>
+  <si>
+    <t>E0049</t>
+  </si>
+  <si>
+    <t>E0050</t>
   </si>
 </sst>
 </file>
@@ -141,7 +225,7 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -152,6 +236,11 @@
       <sz val="12.0"/>
       <color theme="1"/>
       <name val="&quot;Segoe UI&quot;"/>
+    </font>
+    <font>
+      <sz val="12.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;\0022Segoe UI\0022&quot;"/>
     </font>
   </fonts>
   <fills count="2">
@@ -168,12 +257,15 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
@@ -398,9 +490,12 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="5" max="5" width="16.0"/>
-    <col customWidth="1" min="6" max="6" width="19.63"/>
-    <col customWidth="1" min="7" max="7" width="14.5"/>
+    <col customWidth="1" min="2" max="2" width="8.13"/>
+    <col customWidth="1" min="3" max="3" width="22.88"/>
+    <col customWidth="1" min="4" max="4" width="15.63"/>
+    <col customWidth="1" min="5" max="5" width="18.38"/>
+    <col customWidth="1" min="6" max="6" width="32.38"/>
+    <col customWidth="1" min="8" max="8" width="51.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -425,6 +520,7 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="1" t="s">
@@ -442,12 +538,13 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>45698.385416666664</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H2" s="2"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="s">
@@ -465,12 +562,13 @@
       <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="2">
+      <c r="F3" s="3">
         <v>45698.38888888889</v>
       </c>
       <c r="G3" s="1">
         <v>25.0</v>
       </c>
+      <c r="H3" s="2"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
@@ -488,12 +586,13 @@
       <c r="E4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="2">
+      <c r="F4" s="3">
         <v>45700.604166666664</v>
       </c>
       <c r="G4" s="1">
         <v>100.0</v>
       </c>
+      <c r="H4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="s">
@@ -511,12 +610,13 @@
       <c r="E5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F5" s="2">
+      <c r="F5" s="3">
         <v>45703.416666666664</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H5" s="2"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="s">
@@ -534,12 +634,13 @@
       <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="2">
+      <c r="F6" s="3">
         <v>45704.47222222222</v>
       </c>
       <c r="G6" s="1">
         <v>10.0</v>
       </c>
+      <c r="H6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="s">
@@ -557,12 +658,13 @@
       <c r="E7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="2">
+      <c r="F7" s="3">
         <v>45705.697916666664</v>
       </c>
       <c r="G7" s="1">
         <v>100.0</v>
       </c>
+      <c r="H7" s="2"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="s">
@@ -580,12 +682,13 @@
       <c r="E8" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F8" s="2">
+      <c r="F8" s="3">
         <v>45708.375</v>
       </c>
       <c r="G8" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H8" s="2"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="s">
@@ -603,12 +706,13 @@
       <c r="E9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="2">
+      <c r="F9" s="3">
         <v>45710.552083333336</v>
       </c>
       <c r="G9" s="1">
         <v>100.0</v>
       </c>
+      <c r="H9" s="2"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="s">
@@ -626,12 +730,13 @@
       <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="2">
+      <c r="F10" s="3">
         <v>45711.4375</v>
       </c>
       <c r="G10" s="1">
         <v>30.0</v>
       </c>
+      <c r="H10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="s">
@@ -649,12 +754,13 @@
       <c r="E11" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F11" s="2">
+      <c r="F11" s="3">
         <v>45677.364583333336</v>
       </c>
       <c r="G11" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H11" s="2"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="s">
@@ -672,12 +778,13 @@
       <c r="E12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F12" s="2">
+      <c r="F12" s="3">
         <v>45677.375</v>
       </c>
       <c r="G12" s="1">
         <v>15.0</v>
       </c>
+      <c r="H12" s="2"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="s">
@@ -695,12 +802,13 @@
       <c r="E13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="2">
+      <c r="F13" s="3">
         <v>45716.479166666664</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H13" s="2"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="s">
@@ -718,12 +826,13 @@
       <c r="E14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="2">
+      <c r="F14" s="3">
         <v>45717.72222222222</v>
       </c>
       <c r="G14" s="1">
         <v>100.0</v>
       </c>
+      <c r="H14" s="2"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
@@ -741,12 +850,13 @@
       <c r="E15" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F15" s="2">
+      <c r="F15" s="3">
         <v>45718.427083333336</v>
       </c>
       <c r="G15" s="1" t="s">
         <v>10</v>
       </c>
+      <c r="H15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
@@ -764,7 +874,7 @@
       <c r="E16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="2">
+      <c r="F16" s="3">
         <v>45721.520833333336</v>
       </c>
       <c r="G16" s="1">
@@ -787,7 +897,7 @@
       <c r="E17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F17" s="2">
+      <c r="F17" s="3">
         <v>45722.40625</v>
       </c>
       <c r="G17" s="1">
@@ -810,7 +920,7 @@
       <c r="E18" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F18" s="2">
+      <c r="F18" s="3">
         <v>45724.59722222222</v>
       </c>
       <c r="G18" s="1" t="s">
@@ -833,7 +943,7 @@
       <c r="E19" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F19" s="2">
+      <c r="F19" s="3">
         <v>45724.604166666664</v>
       </c>
       <c r="G19" s="1">
@@ -856,7 +966,7 @@
       <c r="E20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F20" s="2">
+      <c r="F20" s="3">
         <v>45727.46527777778</v>
       </c>
       <c r="G20" s="1">
@@ -879,7 +989,7 @@
       <c r="E21" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F21" s="2">
+      <c r="F21" s="3">
         <v>45728.572916666664</v>
       </c>
       <c r="G21" s="1">
@@ -902,7 +1012,7 @@
       <c r="E22" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F22" s="2">
+      <c r="F22" s="3">
         <v>45731.416666666664</v>
       </c>
       <c r="G22" s="1" t="s">
@@ -925,11 +1035,655 @@
       <c r="E23" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F23" s="3">
+      <c r="F23" s="4">
         <v>45732.0</v>
       </c>
       <c r="G23" s="1">
         <v>100.0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B24" s="1">
+        <v>1016.0</v>
+      </c>
+      <c r="C24" s="1">
+        <v>1016001.0</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F24" s="3">
+        <v>45717.427083333336</v>
+      </c>
+      <c r="G24" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="1">
+        <v>1016.0</v>
+      </c>
+      <c r="C25" s="1">
+        <v>1016002.0</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F25" s="3">
+        <v>45721.604166666664</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B26" s="1">
+        <v>1017.0</v>
+      </c>
+      <c r="C26" s="1">
+        <v>1017002.0</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26" s="3">
+        <v>45718.47222222222</v>
+      </c>
+      <c r="G26" s="1">
+        <v>15.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="1">
+        <v>1017.0</v>
+      </c>
+      <c r="C27" s="1">
+        <v>1017002.0</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F27" s="3">
+        <v>45726.697916666664</v>
+      </c>
+      <c r="G27" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" s="1">
+        <v>1018.0</v>
+      </c>
+      <c r="C28" s="1">
+        <v>1018001.0</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F28" s="3">
+        <v>45716.375</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B29" s="1">
+        <v>1018.0</v>
+      </c>
+      <c r="C29" s="1">
+        <v>1018001.0</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="3">
+        <v>45717.4375</v>
+      </c>
+      <c r="G29" s="1">
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="B30" s="1">
+        <v>1019.0</v>
+      </c>
+      <c r="C30" s="1">
+        <v>1019001.0</v>
+      </c>
+      <c r="D30" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F30" s="3">
+        <v>45721.552083333336</v>
+      </c>
+      <c r="G30" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B31" s="1">
+        <v>1020.0</v>
+      </c>
+      <c r="C31" s="1">
+        <v>1020001.0</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F31" s="3">
+        <v>45724.489583333336</v>
+      </c>
+      <c r="G31" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="B32" s="1">
+        <v>1020.0</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1020002.0</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F32" s="3">
+        <v>45728.395833333336</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B33" s="1">
+        <v>1021.0</v>
+      </c>
+      <c r="C33" s="1">
+        <v>1021001.0</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F33" s="3">
+        <v>45726.63888888889</v>
+      </c>
+      <c r="G33" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B34" s="1">
+        <v>1021.0</v>
+      </c>
+      <c r="C34" s="1">
+        <v>1021001.0</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F34" s="3">
+        <v>45726.645833333336</v>
+      </c>
+      <c r="G34" s="1">
+        <v>10.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B35" s="1">
+        <v>1022.0</v>
+      </c>
+      <c r="C35" s="1">
+        <v>1022001.0</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E35" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F35" s="3">
+        <v>45731.416666666664</v>
+      </c>
+      <c r="G35" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" s="1">
+        <v>1023.0</v>
+      </c>
+      <c r="C36" s="1">
+        <v>1023001.0</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F36" s="3">
+        <v>45730.708333333336</v>
+      </c>
+      <c r="G36" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="1">
+        <v>1023.0</v>
+      </c>
+      <c r="C37" s="1">
+        <v>1023002.0</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F37" s="3">
+        <v>45732.385416666664</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B38" s="1">
+        <v>1024.0</v>
+      </c>
+      <c r="C38" s="1">
+        <v>1024001.0</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E38" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F38" s="3">
+        <v>45734.61111111111</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="1">
+        <v>1024.0</v>
+      </c>
+      <c r="C39" s="1">
+        <v>1024001.0</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E39" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3">
+        <v>45734.618055555555</v>
+      </c>
+      <c r="G39" s="1">
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="1">
+        <v>1025.0</v>
+      </c>
+      <c r="C40" s="1">
+        <v>1025001.0</v>
+      </c>
+      <c r="D40" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E40" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F40" s="3">
+        <v>45736.46527777778</v>
+      </c>
+      <c r="G40" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="1">
+        <v>1026.0</v>
+      </c>
+      <c r="C41" s="1">
+        <v>1026001.0</v>
+      </c>
+      <c r="D41" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E41" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F41" s="3">
+        <v>45738.55902777778</v>
+      </c>
+      <c r="G41" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B42" s="1">
+        <v>1027.0</v>
+      </c>
+      <c r="C42" s="1">
+        <v>1027001.0</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E42" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F42" s="3">
+        <v>45737.6875</v>
+      </c>
+      <c r="G42" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="B43" s="1">
+        <v>1027.0</v>
+      </c>
+      <c r="C43" s="1">
+        <v>1027002.0</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E43" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F43" s="3">
+        <v>45739.416666666664</v>
+      </c>
+      <c r="G43" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" s="1">
+        <v>1028.0</v>
+      </c>
+      <c r="C44" s="1">
+        <v>1028001.0</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F44" s="3">
+        <v>45740.40625</v>
+      </c>
+      <c r="G44" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="B45" s="1">
+        <v>1029.0</v>
+      </c>
+      <c r="C45" s="1">
+        <v>1029001.0</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F45" s="3">
+        <v>45741.59375</v>
+      </c>
+      <c r="G45" s="1">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B46" s="1">
+        <v>1030.0</v>
+      </c>
+      <c r="C46" s="1">
+        <v>1030001.0</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F46" s="3">
+        <v>45742.479166666664</v>
+      </c>
+      <c r="G46" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B47" s="1">
+        <v>1031.0</v>
+      </c>
+      <c r="C47" s="1">
+        <v>1031001.0</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E47" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F47" s="3">
+        <v>45743.65277777778</v>
+      </c>
+      <c r="G47" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B48" s="1">
+        <v>1032.0</v>
+      </c>
+      <c r="C48" s="1">
+        <v>1032001.0</v>
+      </c>
+      <c r="D48" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E48" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F48" s="3">
+        <v>45744.71875</v>
+      </c>
+      <c r="G48" s="1">
+        <v>100.0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B49" s="1">
+        <v>1033.0</v>
+      </c>
+      <c r="C49" s="1">
+        <v>1033001.0</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F49" s="3">
+        <v>45745.4375</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B50" s="1">
+        <v>1034.0</v>
+      </c>
+      <c r="C50" s="1">
+        <v>1034001.0</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F50" s="3">
+        <v>45746.375</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B51" s="1">
+        <v>1035.0</v>
+      </c>
+      <c r="C51" s="1">
+        <v>1035001.0</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F51" s="3">
+        <v>45747.555555555555</v>
+      </c>
+      <c r="G51" s="1">
+        <v>10.0</v>
       </c>
     </row>
   </sheetData>
